--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>636.0</v>
+        <v>648.0</v>
       </c>
       <c r="D18" t="n">
         <v>239.0</v>
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>392.0</v>
+        <v>403.0</v>
       </c>
       <c r="D21" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
     </row>
     <row r="22">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>392.0</v>
+        <v>394.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>115.0</v>
+        <v>119.0</v>
       </c>
       <c r="D25" t="n">
         <v>295.0</v>
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="D26" t="n">
         <v>88.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3969.0</v>
+        <v>3973.0</v>
       </c>
       <c r="D34" t="n">
         <v>189.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>954.0</v>
+        <v>960.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1675,7 +1675,7 @@
         <v>504.0</v>
       </c>
       <c r="D88" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>506.0</v>
+        <v>510.0</v>
       </c>
       <c r="D89" t="n">
         <v>133.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
       <c r="D90" t="n">
         <v>112.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="D93" t="n">
         <v>49.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D95" t="n">
         <v>236.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1186.0</v>
+        <v>1192.0</v>
       </c>
       <c r="D6" t="n">
         <v>343.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2219.0</v>
+        <v>2228.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1096.0</v>
+        <v>1099.0</v>
       </c>
     </row>
     <row r="8">
@@ -1406,10 +1406,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>219.0</v>
+        <v>223.0</v>
       </c>
       <c r="D69" t="n">
-        <v>205.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="70">
@@ -1448,7 +1448,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="D72" t="n">
         <v>0.0</v>
@@ -1476,7 +1476,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
       <c r="D74" t="n">
         <v>49.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>176.0</v>
+        <v>178.0</v>
       </c>
       <c r="D30" t="n">
         <v>161.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1297,7 +1297,7 @@
         <v>734.0</v>
       </c>
       <c r="D61" t="n">
-        <v>907.0</v>
+        <v>909.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>1226.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12983.0</v>
+        <v>12998.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2899.0</v>
+        <v>2901.0</v>
       </c>
       <c r="D63" t="n">
-        <v>723.0</v>
+        <v>725.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>1597.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1173.0</v>
+        <v>1174.0</v>
       </c>
     </row>
     <row r="67">
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>296.0</v>
+        <v>298.0</v>
       </c>
       <c r="D90" t="n">
         <v>112.0</v>
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
       <c r="D100" t="n">
         <v>160.0</v>
@@ -1896,7 +1896,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="D104" t="n">
         <v>321.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>648.0</v>
+        <v>650.0</v>
       </c>
       <c r="D18" t="n">
         <v>239.0</v>
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>403.0</v>
+        <v>405.0</v>
       </c>
       <c r="D21" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
     </row>
     <row r="22">
@@ -793,7 +793,7 @@
         <v>119.0</v>
       </c>
       <c r="D25" t="n">
-        <v>295.0</v>
+        <v>297.0</v>
       </c>
     </row>
     <row r="26">
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3973.0</v>
+        <v>3975.0</v>
       </c>
       <c r="D34" t="n">
         <v>189.0</v>
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="D40" t="n">
-        <v>935.0</v>
+        <v>937.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2195.0</v>
+        <v>2198.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>457.0</v>
+        <v>461.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4006.0</v>
+        <v>4007.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>85.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24875.0</v>
+        <v>24878.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1468.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="47">
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1689.0</v>
+        <v>1695.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>757.0</v>
+        <v>759.0</v>
       </c>
       <c r="D51" t="n">
         <v>76.0</v>
@@ -1269,7 +1269,7 @@
         <v>1764.0</v>
       </c>
       <c r="D59" t="n">
-        <v>363.0</v>
+        <v>364.0</v>
       </c>
     </row>
     <row r="60">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1226.0</v>
+        <v>1227.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12998.0</v>
+        <v>13010.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1497.0</v>
+        <v>1498.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2697.0</v>
+        <v>2700.0</v>
       </c>
     </row>
     <row r="65">
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>298.0</v>
+        <v>300.0</v>
       </c>
       <c r="D90" t="n">
         <v>112.0</v>
@@ -1770,10 +1770,10 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>162.0</v>
+        <v>165.0</v>
       </c>
       <c r="D95" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -863,7 +863,7 @@
         <v>178.0</v>
       </c>
       <c r="D30" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="31">
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3975.0</v>
+        <v>3977.0</v>
       </c>
       <c r="D34" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
     </row>
     <row r="35">
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>960.0</v>
+        <v>962.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1171,7 +1171,7 @@
         <v>385.0</v>
       </c>
       <c r="D52" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="53">
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>243.0</v>
+        <v>245.0</v>
       </c>
       <c r="D53" t="n">
         <v>58.0</v>
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>501.0</v>
+        <v>505.0</v>
       </c>
       <c r="D55" t="n">
         <v>140.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
       <c r="D56" t="n">
         <v>150.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1764.0</v>
+        <v>1765.0</v>
       </c>
       <c r="D59" t="n">
         <v>364.0</v>
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1227.0</v>
+        <v>1229.0</v>
       </c>
       <c r="D62" t="n">
         <v>13010.0</v>
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>577.0</v>
+        <v>579.0</v>
       </c>
     </row>
     <row r="68">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>504.0</v>
+        <v>506.0</v>
       </c>
       <c r="D88" t="n">
         <v>289.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="D89" t="n">
         <v>133.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="D93" t="n">
         <v>49.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>840.0</v>
+        <v>847.0</v>
       </c>
       <c r="D96" t="n">
-        <v>475.0</v>
+        <v>479.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>609.0</v>
+        <v>617.0</v>
       </c>
       <c r="D97" t="n">
-        <v>150.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="98">
@@ -1843,7 +1843,7 @@
         <v>227.0</v>
       </c>
       <c r="D100" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="101">
@@ -1899,7 +1899,7 @@
         <v>124.0</v>
       </c>
       <c r="D104" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>936.0</v>
+        <v>938.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3977.0</v>
+        <v>3982.0</v>
       </c>
       <c r="D34" t="n">
         <v>190.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1765.0</v>
+        <v>1772.0</v>
       </c>
       <c r="D59" t="n">
         <v>364.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1640.0</v>
+        <v>1643.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1294,7 +1294,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>734.0</v>
+        <v>736.0</v>
       </c>
       <c r="D61" t="n">
         <v>909.0</v>
@@ -1311,7 +1311,7 @@
         <v>1229.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13010.0</v>
+        <v>13042.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2901.0</v>
+        <v>2902.0</v>
       </c>
       <c r="D63" t="n">
-        <v>725.0</v>
+        <v>726.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1498.0</v>
+        <v>1501.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2700.0</v>
+        <v>2706.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1597.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1174.0</v>
+        <v>1177.0</v>
       </c>
     </row>
     <row r="67">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>511.0</v>
+        <v>516.0</v>
       </c>
       <c r="D89" t="n">
         <v>133.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>300.0</v>
+        <v>303.0</v>
       </c>
       <c r="D90" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="91">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="D93" t="n">
         <v>49.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>938.0</v>
+        <v>939.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>329.0</v>
+        <v>333.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3982.0</v>
+        <v>3984.0</v>
       </c>
       <c r="D34" t="n">
         <v>190.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>385.0</v>
+        <v>386.0</v>
       </c>
       <c r="D52" t="n">
         <v>105.0</v>
@@ -1185,7 +1185,7 @@
         <v>245.0</v>
       </c>
       <c r="D53" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="54">
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>180.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>505.0</v>
+        <v>506.0</v>
       </c>
       <c r="D55" t="n">
         <v>140.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1229.0</v>
+        <v>1230.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13042.0</v>
+        <v>13060.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1501.0</v>
+        <v>1502.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2706.0</v>
+        <v>2709.0</v>
       </c>
     </row>
     <row r="65">
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>506.0</v>
+        <v>507.0</v>
       </c>
       <c r="D88" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>516.0</v>
+        <v>519.0</v>
       </c>
       <c r="D89" t="n">
         <v>133.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>213.0</v>
+        <v>220.0</v>
       </c>
       <c r="D93" t="n">
         <v>49.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>165.0</v>
+        <v>170.0</v>
       </c>
       <c r="D95" t="n">
         <v>237.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>847.0</v>
+        <v>849.0</v>
       </c>
       <c r="D96" t="n">
         <v>479.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>519.0</v>
+        <v>521.0</v>
       </c>
       <c r="D89" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="90">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="D91" t="n">
         <v>65.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="D93" t="n">
         <v>49.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -835,7 +835,7 @@
         <v>253.0</v>
       </c>
       <c r="D28" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="29">
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -860,10 +860,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="D30" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="31">
@@ -1171,7 +1171,7 @@
         <v>386.0</v>
       </c>
       <c r="D52" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="53">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1772.0</v>
+        <v>1779.0</v>
       </c>
       <c r="D59" t="n">
         <v>364.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1230.0</v>
+        <v>1231.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13060.0</v>
+        <v>13070.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2902.0</v>
       </c>
       <c r="D63" t="n">
-        <v>726.0</v>
+        <v>729.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1502.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2709.0</v>
+        <v>2710.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1597.0</v>
+        <v>1598.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1177.0</v>
+        <v>1178.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>579.0</v>
+        <v>582.0</v>
       </c>
     </row>
     <row r="68">
@@ -1395,7 +1395,7 @@
         <v>39.0</v>
       </c>
       <c r="D68" t="n">
-        <v>148.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="69">
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>849.0</v>
+        <v>854.0</v>
       </c>
       <c r="D96" t="n">
         <v>479.0</v>
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>617.0</v>
+        <v>619.0</v>
       </c>
       <c r="D97" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="98">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>227.0</v>
+        <v>229.0</v>
       </c>
       <c r="D100" t="n">
         <v>161.0</v>
@@ -1899,7 +1899,7 @@
         <v>124.0</v>
       </c>
       <c r="D104" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,10 +1910,10 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="D105" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,10 +468,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>993.0</v>
+        <v>994.0</v>
       </c>
       <c r="D2" t="n">
-        <v>86.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>478.0</v>
       </c>
       <c r="D3" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="4">
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="D4" t="n">
-        <v>381.0</v>
+        <v>389.0</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         <v>239.0</v>
       </c>
       <c r="D5" t="n">
-        <v>122.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="6">
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>650.0</v>
+        <v>653.0</v>
       </c>
       <c r="D18" t="n">
-        <v>239.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="19">
@@ -737,7 +737,7 @@
         <v>405.0</v>
       </c>
       <c r="D21" t="n">
-        <v>536.0</v>
+        <v>538.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="D22" t="n">
         <v>291.0</v>
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>394.0</v>
+        <v>395.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>119.0</v>
       </c>
       <c r="D25" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
     </row>
     <row r="26">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>939.0</v>
+        <v>940.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>340.0</v>
+        <v>343.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3984.0</v>
+        <v>3985.0</v>
       </c>
       <c r="D34" t="n">
         <v>190.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>962.0</v>
+        <v>968.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="D40" t="n">
-        <v>937.0</v>
+        <v>943.0</v>
       </c>
     </row>
     <row r="41">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>461.0</v>
+        <v>462.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>147.0</v>
+        <v>150.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4007.0</v>
+        <v>4010.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>85.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24878.0</v>
+        <v>24881.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1472.0</v>
+        <v>1473.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,7 +1098,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>747.0</v>
+        <v>751.0</v>
       </c>
       <c r="D47" t="n">
         <v>1898.0</v>
@@ -1154,10 +1154,10 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>759.0</v>
+        <v>762.0</v>
       </c>
       <c r="D51" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="52">
@@ -1238,10 +1238,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>769.0</v>
+        <v>770.0</v>
       </c>
       <c r="D57" t="n">
-        <v>462.0</v>
+        <v>473.0</v>
       </c>
     </row>
     <row r="58">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>170.0</v>
+        <v>173.0</v>
       </c>
       <c r="D58" t="n">
         <v>176.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1643.0</v>
+        <v>1644.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1231.0</v>
+        <v>1234.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13070.0</v>
+        <v>13085.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1502.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2710.0</v>
+        <v>2712.0</v>
       </c>
     </row>
     <row r="65">
@@ -1689,7 +1689,7 @@
         <v>521.0</v>
       </c>
       <c r="D89" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="90">
@@ -1717,7 +1717,7 @@
         <v>174.0</v>
       </c>
       <c r="D91" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="92">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>395.0</v>
+        <v>394.0</v>
       </c>
     </row>
     <row r="25">
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3985.0</v>
+        <v>3986.0</v>
       </c>
       <c r="D34" t="n">
         <v>190.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>585.0</v>
+        <v>586.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1779.0</v>
+        <v>1785.0</v>
       </c>
       <c r="D59" t="n">
-        <v>364.0</v>
+        <v>366.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1644.0</v>
+        <v>1650.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1234.0</v>
+        <v>1237.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13085.0</v>
+        <v>13099.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2902.0</v>
+        <v>2903.0</v>
       </c>
       <c r="D63" t="n">
-        <v>729.0</v>
+        <v>732.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1502.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2712.0</v>
+        <v>2713.0</v>
       </c>
     </row>
     <row r="65">
@@ -1493,7 +1493,7 @@
         <v>52.0</v>
       </c>
       <c r="D75" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>711.0</v>
+        <v>717.0</v>
       </c>
       <c r="D76" t="n">
-        <v>448.0</v>
+        <v>450.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>512.0</v>
+        <v>520.0</v>
       </c>
       <c r="D77" t="n">
-        <v>473.0</v>
+        <v>476.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,7 +1532,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1855.0</v>
+        <v>1873.0</v>
       </c>
       <c r="D78" t="n">
         <v>551.0</v>
@@ -1546,10 +1546,10 @@
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>342.0</v>
+        <v>345.0</v>
       </c>
       <c r="D79" t="n">
-        <v>524.0</v>
+        <v>530.0</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
       <c r="D90" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="91">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>174.0</v>
+        <v>175.0</v>
       </c>
       <c r="D91" t="n">
         <v>66.0</v>
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>221.0</v>
+        <v>225.0</v>
       </c>
       <c r="D93" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="94">
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="D95" t="n">
         <v>237.0</v>
@@ -1815,7 +1815,7 @@
         <v>97.0</v>
       </c>
       <c r="D98" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="99">
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
     </row>
     <row r="100">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>653.0</v>
+        <v>654.0</v>
       </c>
       <c r="D18" t="n">
         <v>242.0</v>
@@ -723,7 +723,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="21">
@@ -751,7 +751,7 @@
         <v>42.0</v>
       </c>
       <c r="D22" t="n">
-        <v>291.0</v>
+        <v>292.0</v>
       </c>
     </row>
     <row r="23">
@@ -790,10 +790,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="D25" t="n">
-        <v>298.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="26">
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3986.0</v>
+        <v>3988.0</v>
       </c>
       <c r="D34" t="n">
         <v>190.0</v>
@@ -1000,7 +1000,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="D40" t="n">
         <v>943.0</v>
@@ -1168,10 +1168,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>386.0</v>
+        <v>387.0</v>
       </c>
       <c r="D52" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="53">
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,10 +1210,10 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
       <c r="D55" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="56">
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
       <c r="D56" t="n">
         <v>150.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1785.0</v>
+        <v>1789.0</v>
       </c>
       <c r="D59" t="n">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1650.0</v>
+        <v>1651.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>736.0</v>
       </c>
       <c r="D61" t="n">
-        <v>909.0</v>
+        <v>910.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1237.0</v>
+        <v>1239.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13099.0</v>
+        <v>13101.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2903.0</v>
       </c>
       <c r="D63" t="n">
-        <v>732.0</v>
+        <v>733.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1502.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2713.0</v>
+        <v>2717.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1598.0</v>
+        <v>1599.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1178.0</v>
+        <v>1179.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>507.0</v>
+        <v>510.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>522.0</v>
+        <v>526.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="D90" t="n">
         <v>114.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="D91" t="n">
         <v>66.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>225.0</v>
+        <v>235.0</v>
       </c>
       <c r="D93" t="n">
         <v>50.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>854.0</v>
+        <v>855.0</v>
       </c>
       <c r="D96" t="n">
         <v>479.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="D97" t="n">
         <v>154.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>394.0</v>
+        <v>395.0</v>
       </c>
     </row>
     <row r="25">
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="D28" t="n">
         <v>161.0</v>
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>940.0</v>
+        <v>947.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>343.0</v>
+        <v>346.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3988.0</v>
+        <v>3992.0</v>
       </c>
       <c r="D34" t="n">
         <v>190.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1789.0</v>
+        <v>1792.0</v>
       </c>
       <c r="D59" t="n">
-        <v>367.0</v>
+        <v>368.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1651.0</v>
+        <v>1653.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1311,7 +1311,7 @@
         <v>1239.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13101.0</v>
+        <v>13127.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1502.0</v>
+        <v>1503.0</v>
       </c>
       <c r="D64" t="n">
         <v>2717.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>526.0</v>
+        <v>528.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>223.0</v>
+        <v>224.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
       <c r="D100" t="n">
         <v>161.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3992.0</v>
+        <v>3993.0</v>
       </c>
       <c r="D34" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="35">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
       <c r="D90" t="n">
         <v>114.0</v>
@@ -1714,10 +1714,10 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="D91" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="92">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1773,7 +1773,7 @@
         <v>171.0</v>
       </c>
       <c r="D95" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -485,7 +485,7 @@
         <v>478.0</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         <v>194.0</v>
       </c>
       <c r="D4" t="n">
-        <v>389.0</v>
+        <v>394.0</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1192.0</v>
+        <v>1198.0</v>
       </c>
       <c r="D6" t="n">
         <v>343.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2228.0</v>
+        <v>2244.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1099.0</v>
+        <v>1102.0</v>
       </c>
     </row>
     <row r="8">
@@ -569,7 +569,7 @@
         <v>314.0</v>
       </c>
       <c r="D9" t="n">
-        <v>591.0</v>
+        <v>602.0</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +594,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>2799.0</v>
+        <v>2803.0</v>
       </c>
       <c r="D11" t="n">
         <v>568.0</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -622,7 +622,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>912.0</v>
+        <v>926.0</v>
       </c>
       <c r="D13" t="n">
         <v>339.0</v>
@@ -636,10 +636,10 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>616.0</v>
+        <v>629.0</v>
       </c>
       <c r="D14" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="15">
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>720.0</v>
+        <v>733.0</v>
       </c>
       <c r="D15" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="16">
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9317.0</v>
+        <v>9328.0</v>
       </c>
       <c r="D17" t="n">
-        <v>907.0</v>
+        <v>909.0</v>
       </c>
     </row>
     <row r="18">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>405.0</v>
+        <v>419.0</v>
       </c>
       <c r="D21" t="n">
         <v>538.0</v>
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>120.0</v>
+        <v>123.0</v>
       </c>
       <c r="D25" t="n">
         <v>300.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="D30" t="n">
         <v>163.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>265.0</v>
+        <v>266.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1241,7 +1241,7 @@
         <v>770.0</v>
       </c>
       <c r="D57" t="n">
-        <v>473.0</v>
+        <v>478.0</v>
       </c>
     </row>
     <row r="58">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1792.0</v>
+        <v>1794.0</v>
       </c>
       <c r="D59" t="n">
-        <v>368.0</v>
+        <v>369.0</v>
       </c>
     </row>
     <row r="60">
@@ -1297,7 +1297,7 @@
         <v>736.0</v>
       </c>
       <c r="D61" t="n">
-        <v>910.0</v>
+        <v>911.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1239.0</v>
+        <v>1242.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13127.0</v>
+        <v>13143.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2903.0</v>
+        <v>2907.0</v>
       </c>
       <c r="D63" t="n">
-        <v>733.0</v>
+        <v>734.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1503.0</v>
+        <v>1504.0</v>
       </c>
       <c r="D64" t="n">
         <v>2717.0</v>
@@ -1367,7 +1367,7 @@
         <v>1599.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1179.0</v>
+        <v>1181.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>582.0</v>
+        <v>585.0</v>
       </c>
     </row>
     <row r="68">
@@ -1395,7 +1395,7 @@
         <v>39.0</v>
       </c>
       <c r="D68" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="69">
@@ -1406,7 +1406,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>223.0</v>
+        <v>225.0</v>
       </c>
       <c r="D69" t="n">
         <v>207.0</v>
@@ -1476,7 +1476,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="D74" t="n">
         <v>49.0</v>
@@ -1787,7 +1787,7 @@
         <v>855.0</v>
       </c>
       <c r="D96" t="n">
-        <v>479.0</v>
+        <v>483.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>620.0</v>
+        <v>622.0</v>
       </c>
       <c r="D97" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="98">
@@ -1857,7 +1857,7 @@
         <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="102">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>947.0</v>
+        <v>949.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>968.0</v>
+        <v>973.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>943.0</v>
+        <v>948.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>186.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2198.0</v>
+        <v>2200.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>150.0</v>
+        <v>154.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4010.0</v>
+        <v>4013.0</v>
       </c>
     </row>
     <row r="44">
@@ -1070,10 +1070,10 @@
         <v>68</v>
       </c>
       <c r="C45" t="n">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24881.0</v>
+        <v>24883.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,7 +1084,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D46" t="n">
         <v>1473.0</v>
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1695.0</v>
+        <v>1703.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1143,7 +1143,7 @@
         <v>25.0</v>
       </c>
       <c r="D50" t="n">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>762.0</v>
+        <v>766.0</v>
       </c>
       <c r="D51" t="n">
         <v>77.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1794.0</v>
+        <v>1796.0</v>
       </c>
       <c r="D59" t="n">
         <v>369.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1653.0</v>
+        <v>1656.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1311,7 +1311,7 @@
         <v>1242.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13143.0</v>
+        <v>13159.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2907.0</v>
       </c>
       <c r="D63" t="n">
-        <v>734.0</v>
+        <v>736.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1504.0</v>
+        <v>1506.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2717.0</v>
+        <v>2720.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1599.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1181.0</v>
+        <v>1183.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>585.0</v>
+        <v>587.0</v>
       </c>
     </row>
     <row r="68">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>529.0</v>
+        <v>531.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
     </row>
     <row r="100">
@@ -1843,7 +1843,7 @@
         <v>233.0</v>
       </c>
       <c r="D100" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="101">
@@ -1868,7 +1868,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>108.0</v>
+        <v>110.0</v>
       </c>
       <c r="D102" t="n">
         <v>201.0</v>
@@ -1913,7 +1913,7 @@
         <v>90.0</v>
       </c>
       <c r="D105" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>654.0</v>
+        <v>673.0</v>
       </c>
       <c r="D18" t="n">
         <v>242.0</v>
@@ -751,7 +751,7 @@
         <v>42.0</v>
       </c>
       <c r="D22" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
     </row>
     <row r="23">
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3993.0</v>
+        <v>3998.0</v>
       </c>
       <c r="D34" t="n">
         <v>191.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
       <c r="D56" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="57">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1796.0</v>
+        <v>1798.0</v>
       </c>
       <c r="D59" t="n">
         <v>369.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1656.0</v>
+        <v>1668.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1242.0</v>
+        <v>1245.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13159.0</v>
+        <v>13160.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1506.0</v>
+        <v>1507.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2720.0</v>
+        <v>2721.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1599.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1183.0</v>
+        <v>1185.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>511.0</v>
+        <v>513.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>855.0</v>
+        <v>856.0</v>
       </c>
       <c r="D96" t="n">
-        <v>483.0</v>
+        <v>484.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>949.0</v>
+        <v>950.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>3998.0</v>
+        <v>4000.0</v>
       </c>
       <c r="D34" t="n">
         <v>191.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>266.0</v>
+        <v>268.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>587.0</v>
+        <v>595.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1798.0</v>
+        <v>1799.0</v>
       </c>
       <c r="D59" t="n">
         <v>369.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1668.0</v>
+        <v>1677.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>736.0</v>
       </c>
       <c r="D61" t="n">
-        <v>911.0</v>
+        <v>912.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1245.0</v>
+        <v>1266.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13160.0</v>
+        <v>13198.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2907.0</v>
       </c>
       <c r="D63" t="n">
-        <v>736.0</v>
+        <v>737.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1507.0</v>
+        <v>1508.0</v>
       </c>
       <c r="D64" t="n">
         <v>2721.0</v>
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="D65" t="n">
         <v>26.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>513.0</v>
+        <v>515.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>532.0</v>
+        <v>536.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,10 +468,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>994.0</v>
+        <v>1008.0</v>
       </c>
       <c r="D2" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>478.0</v>
+        <v>487.0</v>
       </c>
       <c r="D3" t="n">
         <v>72.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>194.0</v>
+        <v>201.0</v>
       </c>
       <c r="D4" t="n">
-        <v>394.0</v>
+        <v>397.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,10 +510,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="D5" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="6">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>950.0</v>
+        <v>954.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4000.0</v>
+        <v>4002.0</v>
       </c>
       <c r="D34" t="n">
         <v>191.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>387.0</v>
+        <v>389.0</v>
       </c>
       <c r="D52" t="n">
         <v>107.0</v>
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="D53" t="n">
         <v>59.0</v>
@@ -1213,7 +1213,7 @@
         <v>508.0</v>
       </c>
       <c r="D55" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="56">
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>770.0</v>
+        <v>798.0</v>
       </c>
       <c r="D57" t="n">
         <v>478.0</v>
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>173.0</v>
+        <v>177.0</v>
       </c>
       <c r="D58" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="59">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1266.0</v>
+        <v>1268.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13198.0</v>
+        <v>13208.0</v>
       </c>
     </row>
     <row r="63">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>536.0</v>
+        <v>549.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1717,7 +1717,7 @@
         <v>177.0</v>
       </c>
       <c r="D91" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="92">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>235.0</v>
+        <v>242.0</v>
       </c>
       <c r="D93" t="n">
         <v>50.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>856.0</v>
+        <v>860.0</v>
       </c>
       <c r="D96" t="n">
-        <v>484.0</v>
+        <v>485.0</v>
       </c>
     </row>
     <row r="97">
@@ -1801,7 +1801,7 @@
         <v>622.0</v>
       </c>
       <c r="D97" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,10 +524,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1198.0</v>
+        <v>1202.0</v>
       </c>
       <c r="D6" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2244.0</v>
+        <v>2255.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1102.0</v>
+        <v>1104.0</v>
       </c>
     </row>
     <row r="8">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>954.0</v>
+        <v>956.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>349.0</v>
+        <v>350.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4002.0</v>
+        <v>4004.0</v>
       </c>
       <c r="D34" t="n">
         <v>191.0</v>
@@ -1406,10 +1406,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>225.0</v>
+        <v>227.0</v>
       </c>
       <c r="D69" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="70">
@@ -1420,10 +1420,10 @@
         <v>93</v>
       </c>
       <c r="C70" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="D70" t="n">
-        <v>114.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="71">
@@ -1448,7 +1448,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="D72" t="n">
         <v>0.0</v>
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>307.0</v>
+        <v>308.0</v>
       </c>
       <c r="D74" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="75">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>549.0</v>
+        <v>550.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1717,7 +1717,7 @@
         <v>177.0</v>
       </c>
       <c r="D91" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="92">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="D93" t="n">
         <v>50.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1773,7 +1773,7 @@
         <v>171.0</v>
       </c>
       <c r="D95" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>1008.0</v>
+        <v>1009.0</v>
       </c>
       <c r="D2" t="n">
         <v>100.0</v>
@@ -832,10 +832,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="D28" t="n">
-        <v>161.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="29">
@@ -1255,7 +1255,7 @@
         <v>177.0</v>
       </c>
       <c r="D58" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1799.0</v>
+        <v>1805.0</v>
       </c>
       <c r="D59" t="n">
         <v>369.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1677.0</v>
+        <v>1682.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>736.0</v>
       </c>
       <c r="D61" t="n">
-        <v>912.0</v>
+        <v>914.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1268.0</v>
+        <v>1276.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13208.0</v>
+        <v>13225.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2907.0</v>
       </c>
       <c r="D63" t="n">
-        <v>737.0</v>
+        <v>738.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1508.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2721.0</v>
+        <v>2724.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1599.0</v>
+        <v>1600.0</v>
       </c>
       <c r="D66" t="n">
         <v>1185.0</v>
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>587.0</v>
+        <v>592.0</v>
       </c>
     </row>
     <row r="68">
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
       <c r="D100" t="n">
         <v>162.0</v>
@@ -1896,10 +1896,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="D104" t="n">
-        <v>323.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -737,7 +737,7 @@
         <v>419.0</v>
       </c>
       <c r="D21" t="n">
-        <v>538.0</v>
+        <v>541.0</v>
       </c>
     </row>
     <row r="22">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>123.0</v>
       </c>
       <c r="D25" t="n">
-        <v>300.0</v>
+        <v>303.0</v>
       </c>
     </row>
     <row r="26">
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4004.0</v>
+        <v>4005.0</v>
       </c>
       <c r="D34" t="n">
         <v>191.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>973.0</v>
+        <v>976.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>269.0</v>
+        <v>271.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>597.0</v>
+        <v>616.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1003,7 +1003,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>948.0</v>
+        <v>953.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2200.0</v>
+        <v>2205.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>463.0</v>
+        <v>466.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,7 +1042,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>154.0</v>
+        <v>160.0</v>
       </c>
       <c r="D43" t="n">
         <v>4013.0</v>
@@ -1073,7 +1073,7 @@
         <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24883.0</v>
+        <v>24884.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>10.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1473.0</v>
+        <v>1474.0</v>
       </c>
     </row>
     <row r="47">
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1703.0</v>
+        <v>1707.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>766.0</v>
+        <v>769.0</v>
       </c>
       <c r="D51" t="n">
         <v>77.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
       <c r="D52" t="n">
         <v>107.0</v>
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="D53" t="n">
         <v>59.0</v>
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>508.0</v>
+        <v>511.0</v>
       </c>
       <c r="D55" t="n">
         <v>143.0</v>
@@ -1269,7 +1269,7 @@
         <v>1805.0</v>
       </c>
       <c r="D59" t="n">
-        <v>369.0</v>
+        <v>365.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1682.0</v>
+        <v>1686.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1276.0</v>
+        <v>1296.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13225.0</v>
+        <v>13234.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2907.0</v>
       </c>
       <c r="D63" t="n">
-        <v>738.0</v>
+        <v>699.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1508.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2724.0</v>
+        <v>2725.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1600.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1185.0</v>
+        <v>1184.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>550.0</v>
+        <v>553.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1787,7 +1787,7 @@
         <v>860.0</v>
       </c>
       <c r="D96" t="n">
-        <v>485.0</v>
+        <v>487.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>622.0</v>
+        <v>626.0</v>
       </c>
       <c r="D97" t="n">
         <v>156.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4005.0</v>
+        <v>4007.0</v>
       </c>
       <c r="D34" t="n">
         <v>191.0</v>
@@ -1577,7 +1577,7 @@
         <v>6.0</v>
       </c>
       <c r="D81" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="82">
@@ -1630,7 +1630,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D85" t="n">
         <v>19.0</v>
@@ -1644,10 +1644,10 @@
         <v>109</v>
       </c>
       <c r="C86" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="D86" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="87">
@@ -1661,7 +1661,7 @@
         <v>12.0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="88">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>516.0</v>
+        <v>518.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>553.0</v>
+        <v>555.0</v>
       </c>
       <c r="D89" t="n">
         <v>136.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>243.0</v>
+        <v>246.0</v>
       </c>
       <c r="D93" t="n">
         <v>50.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,10 +524,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1202.0</v>
+        <v>1209.0</v>
       </c>
       <c r="D6" t="n">
-        <v>344.0</v>
+        <v>345.0</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2255.0</v>
+        <v>2263.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1104.0</v>
+        <v>1107.0</v>
       </c>
     </row>
     <row r="8">
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4007.0</v>
+        <v>4015.0</v>
       </c>
       <c r="D34" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
     </row>
     <row r="35">
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>271.0</v>
+        <v>273.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>616.0</v>
+        <v>645.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1805.0</v>
+        <v>1809.0</v>
       </c>
       <c r="D59" t="n">
         <v>365.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1686.0</v>
+        <v>1707.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>736.0</v>
+        <v>737.0</v>
       </c>
       <c r="D61" t="n">
-        <v>914.0</v>
+        <v>916.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1296.0</v>
+        <v>1299.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13234.0</v>
+        <v>13273.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2907.0</v>
       </c>
       <c r="D63" t="n">
-        <v>699.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1508.0</v>
+        <v>1510.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2725.0</v>
+        <v>2728.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1600.0</v>
+        <v>1601.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1184.0</v>
+        <v>1185.0</v>
       </c>
     </row>
     <row r="67">
@@ -1406,10 +1406,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="D69" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="70">
@@ -1476,7 +1476,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>308.0</v>
+        <v>310.0</v>
       </c>
       <c r="D74" t="n">
         <v>51.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>518.0</v>
+        <v>521.0</v>
       </c>
       <c r="D88" t="n">
         <v>290.0</v>
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>555.0</v>
+        <v>565.0</v>
       </c>
       <c r="D89" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="90">
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>307.0</v>
+        <v>310.0</v>
       </c>
       <c r="D90" t="n">
         <v>114.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>246.0</v>
+        <v>250.0</v>
       </c>
       <c r="D93" t="n">
         <v>50.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="D95" t="n">
         <v>239.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>956.0</v>
+        <v>959.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>390.0</v>
+        <v>392.0</v>
       </c>
       <c r="D52" t="n">
         <v>107.0</v>
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="55">
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>442.0</v>
+        <v>443.0</v>
       </c>
       <c r="D56" t="n">
         <v>151.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1299.0</v>
+        <v>1320.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13273.0</v>
+        <v>13287.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2907.0</v>
+        <v>2909.0</v>
       </c>
       <c r="D63" t="n">
-        <v>700.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1510.0</v>
+        <v>1512.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2728.0</v>
+        <v>2733.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1601.0</v>
+        <v>1603.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1185.0</v>
+        <v>1186.0</v>
       </c>
     </row>
     <row r="67">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>565.0</v>
+        <v>566.0</v>
       </c>
       <c r="D89" t="n">
         <v>138.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>860.0</v>
+        <v>864.0</v>
       </c>
       <c r="D96" t="n">
         <v>487.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="D88" t="n">
-        <v>290.0</v>
+        <v>291.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>566.0</v>
+        <v>567.0</v>
       </c>
       <c r="D89" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="90">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,10 +552,10 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>589.0</v>
+        <v>601.0</v>
       </c>
       <c r="D8" t="n">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="9">
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>314.0</v>
+        <v>330.0</v>
       </c>
       <c r="D9" t="n">
-        <v>602.0</v>
+        <v>605.0</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +594,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>2803.0</v>
+        <v>2807.0</v>
       </c>
       <c r="D11" t="n">
         <v>568.0</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>246.0</v>
+        <v>248.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>673.0</v>
+        <v>681.0</v>
       </c>
       <c r="D18" t="n">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
     </row>
     <row r="19">
@@ -720,10 +720,10 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="D20" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>419.0</v>
+        <v>430.0</v>
       </c>
       <c r="D21" t="n">
-        <v>541.0</v>
+        <v>547.0</v>
       </c>
     </row>
     <row r="22">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,10 +790,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="D25" t="n">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
     </row>
     <row r="26">
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="D26" t="n">
         <v>88.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="D30" t="n">
         <v>163.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4015.0</v>
+        <v>4017.0</v>
       </c>
       <c r="D34" t="n">
         <v>192.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1809.0</v>
+        <v>1814.0</v>
       </c>
       <c r="D59" t="n">
-        <v>365.0</v>
+        <v>366.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1707.0</v>
+        <v>1711.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>737.0</v>
       </c>
       <c r="D61" t="n">
-        <v>916.0</v>
+        <v>918.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1320.0</v>
+        <v>1331.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13287.0</v>
+        <v>13296.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1512.0</v>
+        <v>1513.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2733.0</v>
+        <v>2734.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1603.0</v>
+        <v>1604.0</v>
       </c>
       <c r="D66" t="n">
         <v>1186.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>235.0</v>
+        <v>237.0</v>
       </c>
       <c r="D100" t="n">
         <v>162.0</v>
@@ -1868,7 +1868,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
       <c r="D102" t="n">
         <v>201.0</v>
@@ -1910,10 +1910,10 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="D105" t="n">
-        <v>190.0</v>
+        <v>193.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4017.0</v>
+        <v>4018.0</v>
       </c>
       <c r="D34" t="n">
         <v>192.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>976.0</v>
+        <v>981.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1003,7 +1003,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>953.0</v>
+        <v>955.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2205.0</v>
+        <v>2206.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>160.0</v>
+        <v>168.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4013.0</v>
+        <v>4015.0</v>
       </c>
     </row>
     <row r="44">
@@ -1059,7 +1059,7 @@
         <v>30.0</v>
       </c>
       <c r="D44" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24884.0</v>
+        <v>24885.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>10.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1474.0</v>
+        <v>1476.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,10 +1098,10 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>751.0</v>
+        <v>753.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1898.0</v>
+        <v>1899.0</v>
       </c>
     </row>
     <row r="48">
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1707.0</v>
+        <v>1713.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1143,7 +1143,7 @@
         <v>25.0</v>
       </c>
       <c r="D50" t="n">
-        <v>61.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,10 +1154,10 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>769.0</v>
+        <v>772.0</v>
       </c>
       <c r="D51" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="52">
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>247.0</v>
+        <v>249.0</v>
       </c>
       <c r="D53" t="n">
         <v>59.0</v>
@@ -1311,7 +1311,7 @@
         <v>1331.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13296.0</v>
+        <v>13314.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2909.0</v>
+        <v>2910.0</v>
       </c>
       <c r="D63" t="n">
         <v>704.0</v>
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1513.0</v>
+        <v>1514.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2734.0</v>
+        <v>2739.0</v>
       </c>
     </row>
     <row r="65">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>592.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="68">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>522.0</v>
+        <v>524.0</v>
       </c>
       <c r="D88" t="n">
         <v>291.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>567.0</v>
+        <v>571.0</v>
       </c>
       <c r="D89" t="n">
         <v>139.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>310.0</v>
+        <v>312.0</v>
       </c>
       <c r="D90" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="91">
@@ -1801,7 +1801,7 @@
         <v>626.0</v>
       </c>
       <c r="D97" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="98">
@@ -1896,7 +1896,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>125.0</v>
+        <v>127.0</v>
       </c>
       <c r="D104" t="n">
         <v>325.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>959.0</v>
+        <v>961.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4018.0</v>
+        <v>4022.0</v>
       </c>
       <c r="D34" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
     </row>
     <row r="35">
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>275.0</v>
+        <v>283.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>645.0</v>
+        <v>658.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1003,7 +1003,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>955.0</v>
+        <v>953.0</v>
       </c>
     </row>
     <row r="41">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1814.0</v>
+        <v>1827.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1331.0</v>
+        <v>1340.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13314.0</v>
+        <v>13336.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1514.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2739.0</v>
+        <v>2740.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1604.0</v>
+        <v>1605.0</v>
       </c>
       <c r="D66" t="n">
         <v>1186.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>571.0</v>
+        <v>575.0</v>
       </c>
       <c r="D89" t="n">
         <v>139.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -622,10 +622,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>926.0</v>
+        <v>954.0</v>
       </c>
       <c r="D13" t="n">
-        <v>339.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="14">
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>629.0</v>
+        <v>644.0</v>
       </c>
       <c r="D14" t="n">
         <v>120.0</v>
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>733.0</v>
+        <v>743.0</v>
       </c>
       <c r="D15" t="n">
-        <v>183.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="16">
@@ -664,10 +664,10 @@
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="D16" t="n">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="17">
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9328.0</v>
+        <v>9375.0</v>
       </c>
       <c r="D17" t="n">
-        <v>909.0</v>
+        <v>911.0</v>
       </c>
     </row>
     <row r="18">
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>681.0</v>
+        <v>683.0</v>
       </c>
       <c r="D18" t="n">
         <v>244.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>430.0</v>
+        <v>443.0</v>
       </c>
       <c r="D21" t="n">
         <v>547.0</v>
@@ -790,10 +790,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="D25" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         <v>256.0</v>
       </c>
       <c r="D28" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
     </row>
     <row r="29">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>961.0</v>
+        <v>963.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>981.0</v>
+        <v>982.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1711.0</v>
+        <v>1749.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>737.0</v>
       </c>
       <c r="D61" t="n">
-        <v>918.0</v>
+        <v>919.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1340.0</v>
+        <v>1373.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13336.0</v>
+        <v>13351.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1514.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2740.0</v>
+        <v>2742.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1605.0</v>
+        <v>1610.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1186.0</v>
+        <v>1189.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="D88" t="n">
         <v>291.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>575.0</v>
+        <v>675.0</v>
       </c>
       <c r="D89" t="n">
         <v>139.0</v>
@@ -1717,7 +1717,7 @@
         <v>177.0</v>
       </c>
       <c r="D91" t="n">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="92">
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>250.0</v>
+        <v>272.0</v>
       </c>
       <c r="D93" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>172.0</v>
+        <v>174.0</v>
       </c>
       <c r="D95" t="n">
         <v>239.0</v>
@@ -1913,7 +1913,7 @@
         <v>91.0</v>
       </c>
       <c r="D105" t="n">
-        <v>193.0</v>
+        <v>196.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>354.0</v>
+        <v>357.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4022.0</v>
+        <v>4023.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>658.0</v>
+        <v>681.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>392.0</v>
+        <v>393.0</v>
       </c>
       <c r="D52" t="n">
         <v>107.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="D55" t="n">
         <v>143.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="D56" t="n">
         <v>151.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1827.0</v>
+        <v>1832.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1749.0</v>
+        <v>1751.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>737.0</v>
+        <v>738.0</v>
       </c>
       <c r="D61" t="n">
-        <v>919.0</v>
+        <v>921.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1373.0</v>
+        <v>1377.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13351.0</v>
+        <v>13374.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1514.0</v>
+        <v>1515.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2742.0</v>
+        <v>2744.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1610.0</v>
+        <v>1611.0</v>
       </c>
       <c r="D66" t="n">
         <v>1189.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>675.0</v>
+        <v>691.0</v>
       </c>
       <c r="D89" t="n">
         <v>139.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>177.0</v>
+        <v>180.0</v>
       </c>
       <c r="D91" t="n">
         <v>71.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>272.0</v>
+        <v>278.0</v>
       </c>
       <c r="D93" t="n">
         <v>51.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>864.0</v>
+        <v>865.0</v>
       </c>
       <c r="D96" t="n">
         <v>487.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>626.0</v>
+        <v>627.0</v>
       </c>
       <c r="D97" t="n">
         <v>157.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>963.0</v>
+        <v>969.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4023.0</v>
+        <v>4026.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>691.0</v>
+        <v>705.0</v>
       </c>
       <c r="D89" t="n">
         <v>139.0</v>
@@ -1703,7 +1703,7 @@
         <v>312.0</v>
       </c>
       <c r="D90" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="91">
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>174.0</v>
+        <v>175.0</v>
       </c>
       <c r="D95" t="n">
         <v>239.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>1009.0</v>
+        <v>1014.0</v>
       </c>
       <c r="D2" t="n">
         <v>100.0</v>
@@ -482,10 +482,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
       <c r="D3" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="4">
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="D4" t="n">
-        <v>397.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,10 +510,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="D5" t="n">
-        <v>130.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="6">
@@ -1238,10 +1238,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>798.0</v>
+        <v>801.0</v>
       </c>
       <c r="D57" t="n">
-        <v>478.0</v>
+        <v>483.0</v>
       </c>
     </row>
     <row r="58">
@@ -1255,7 +1255,7 @@
         <v>177.0</v>
       </c>
       <c r="D58" t="n">
-        <v>178.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1832.0</v>
+        <v>1834.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1751.0</v>
+        <v>1754.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1311,7 +1311,7 @@
         <v>1377.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13374.0</v>
+        <v>13384.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2910.0</v>
+        <v>2912.0</v>
       </c>
       <c r="D63" t="n">
-        <v>704.0</v>
+        <v>705.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1515.0</v>
+        <v>1516.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2744.0</v>
+        <v>2748.0</v>
       </c>
     </row>
     <row r="65">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>717.0</v>
+        <v>731.0</v>
       </c>
       <c r="D76" t="n">
-        <v>450.0</v>
+        <v>452.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>520.0</v>
+        <v>533.0</v>
       </c>
       <c r="D77" t="n">
-        <v>476.0</v>
+        <v>481.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,7 +1532,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1873.0</v>
+        <v>1926.0</v>
       </c>
       <c r="D78" t="n">
         <v>551.0</v>
@@ -1546,10 +1546,10 @@
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="D79" t="n">
-        <v>530.0</v>
+        <v>533.0</v>
       </c>
     </row>
     <row r="80">
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>865.0</v>
+        <v>867.0</v>
       </c>
       <c r="D96" t="n">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>683.0</v>
+        <v>705.0</v>
       </c>
       <c r="D18" t="n">
         <v>244.0</v>
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="20">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>443.0</v>
+        <v>458.0</v>
       </c>
       <c r="D21" t="n">
         <v>547.0</v>
@@ -751,7 +751,7 @@
         <v>42.0</v>
       </c>
       <c r="D22" t="n">
-        <v>293.0</v>
+        <v>296.0</v>
       </c>
     </row>
     <row r="23">
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="D25" t="n">
         <v>306.0</v>
@@ -832,10 +832,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="D28" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="29">
@@ -860,10 +860,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>181.0</v>
+        <v>185.0</v>
       </c>
       <c r="D30" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
     </row>
     <row r="31">
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>982.0</v>
+        <v>984.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>681.0</v>
+        <v>687.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1003,7 +1003,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>953.0</v>
+        <v>955.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>188.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2206.0</v>
+        <v>2212.0</v>
       </c>
     </row>
     <row r="42">
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>168.0</v>
+        <v>171.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4015.0</v>
+        <v>4016.0</v>
       </c>
     </row>
     <row r="44">
@@ -1059,7 +1059,7 @@
         <v>30.0</v>
       </c>
       <c r="D44" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24885.0</v>
+        <v>24886.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>10.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1476.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,7 +1098,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>753.0</v>
+        <v>761.0</v>
       </c>
       <c r="D47" t="n">
         <v>1899.0</v>
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1713.0</v>
+        <v>1720.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1143,7 +1143,7 @@
         <v>25.0</v>
       </c>
       <c r="D50" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>772.0</v>
+        <v>773.0</v>
       </c>
       <c r="D51" t="n">
         <v>78.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1834.0</v>
+        <v>1842.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1754.0</v>
+        <v>1759.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1377.0</v>
+        <v>1387.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13384.0</v>
+        <v>13386.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2912.0</v>
+        <v>2914.0</v>
       </c>
       <c r="D63" t="n">
         <v>705.0</v>
@@ -1339,7 +1339,7 @@
         <v>1516.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2748.0</v>
+        <v>2752.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1611.0</v>
+        <v>1612.0</v>
       </c>
       <c r="D66" t="n">
         <v>1189.0</v>
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>596.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="68">
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>705.0</v>
+        <v>725.0</v>
       </c>
       <c r="D89" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="90">
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
       <c r="D100" t="n">
         <v>162.0</v>
@@ -1896,10 +1896,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>127.0</v>
+        <v>130.0</v>
       </c>
       <c r="D104" t="n">
-        <v>325.0</v>
+        <v>326.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="D105" t="n">
         <v>196.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>969.0</v>
+        <v>972.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4026.0</v>
+        <v>4027.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>284.0</v>
+        <v>291.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>444.0</v>
+        <v>445.0</v>
       </c>
       <c r="D56" t="n">
         <v>151.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1759.0</v>
+        <v>1787.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1387.0</v>
+        <v>1403.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13386.0</v>
+        <v>13412.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1516.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2752.0</v>
+        <v>2756.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1612.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1189.0</v>
+        <v>1190.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="D88" t="n">
         <v>291.0</v>
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>725.0</v>
+        <v>757.0</v>
       </c>
       <c r="D89" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="90">
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="D90" t="n">
         <v>116.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>180.0</v>
+        <v>182.0</v>
       </c>
       <c r="D91" t="n">
         <v>71.0</v>
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>278.0</v>
+        <v>284.0</v>
       </c>
       <c r="D93" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="D95" t="n">
         <v>239.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>705.0</v>
+        <v>711.0</v>
       </c>
       <c r="D18" t="n">
         <v>244.0</v>
@@ -723,7 +723,7 @@
         <v>80.0</v>
       </c>
       <c r="D20" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
     </row>
     <row r="21">
@@ -737,7 +737,7 @@
         <v>458.0</v>
       </c>
       <c r="D21" t="n">
-        <v>547.0</v>
+        <v>548.0</v>
       </c>
     </row>
     <row r="22">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>972.0</v>
+        <v>974.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4027.0</v>
+        <v>4028.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1842.0</v>
+        <v>1857.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1787.0</v>
+        <v>1793.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>738.0</v>
       </c>
       <c r="D61" t="n">
-        <v>921.0</v>
+        <v>923.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1403.0</v>
+        <v>1413.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13412.0</v>
+        <v>13427.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1516.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2756.0</v>
+        <v>2758.0</v>
       </c>
     </row>
     <row r="65">
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>757.0</v>
+        <v>822.0</v>
       </c>
       <c r="D89" t="n">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="90">
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>313.0</v>
+        <v>315.0</v>
       </c>
       <c r="D90" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="91">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>284.0</v>
+        <v>302.0</v>
       </c>
       <c r="D93" t="n">
         <v>52.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>601.0</v>
+        <v>603.0</v>
       </c>
       <c r="D8" t="n">
         <v>161.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="D9" t="n">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>248.0</v>
+        <v>255.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4028.0</v>
+        <v>4029.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>687.0</v>
+        <v>709.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1168,10 +1168,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>393.0</v>
+        <v>395.0</v>
       </c>
       <c r="D52" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
     </row>
     <row r="53">
@@ -1213,7 +1213,7 @@
         <v>512.0</v>
       </c>
       <c r="D55" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="56">
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>445.0</v>
+        <v>446.0</v>
       </c>
       <c r="D56" t="n">
         <v>151.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1857.0</v>
+        <v>1861.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1413.0</v>
+        <v>1417.0</v>
       </c>
       <c r="D62" t="n">
         <v>13427.0</v>
@@ -1325,7 +1325,7 @@
         <v>2914.0</v>
       </c>
       <c r="D63" t="n">
-        <v>705.0</v>
+        <v>706.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1516.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2758.0</v>
+        <v>2760.0</v>
       </c>
     </row>
     <row r="65">
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="D88" t="n">
-        <v>291.0</v>
+        <v>293.0</v>
       </c>
     </row>
     <row r="89">
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>176.0</v>
+        <v>178.0</v>
       </c>
       <c r="D95" t="n">
         <v>239.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>867.0</v>
+        <v>869.0</v>
       </c>
       <c r="D96" t="n">
         <v>489.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="D97" t="n">
         <v>157.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>974.0</v>
+        <v>975.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4029.0</v>
+        <v>4031.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>528.0</v>
+        <v>530.0</v>
       </c>
       <c r="D88" t="n">
-        <v>293.0</v>
+        <v>294.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>822.0</v>
+        <v>830.0</v>
       </c>
       <c r="D89" t="n">
         <v>144.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="D90" t="n">
         <v>117.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="D95" t="n">
         <v>239.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>709.0</v>
+        <v>710.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1793.0</v>
+        <v>1803.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>738.0</v>
+        <v>739.0</v>
       </c>
       <c r="D61" t="n">
-        <v>923.0</v>
+        <v>925.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1417.0</v>
+        <v>1440.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13427.0</v>
+        <v>13445.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2914.0</v>
       </c>
       <c r="D63" t="n">
-        <v>706.0</v>
+        <v>707.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1516.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2760.0</v>
+        <v>2761.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1612.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1190.0</v>
+        <v>1196.0</v>
       </c>
     </row>
     <row r="67">
@@ -1504,7 +1504,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>731.0</v>
+        <v>733.0</v>
       </c>
       <c r="D76" t="n">
         <v>452.0</v>
@@ -1532,7 +1532,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1926.0</v>
+        <v>1932.0</v>
       </c>
       <c r="D78" t="n">
         <v>551.0</v>
@@ -1675,7 +1675,7 @@
         <v>530.0</v>
       </c>
       <c r="D88" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
     </row>
     <row r="89">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>358.0</v>
+        <v>359.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>984.0</v>
+        <v>989.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>710.0</v>
+        <v>737.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1003,7 +1003,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>955.0</v>
+        <v>965.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>188.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2212.0</v>
+        <v>2213.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>171.0</v>
+        <v>176.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4016.0</v>
+        <v>4017.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24886.0</v>
+        <v>24888.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>10.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1477.0</v>
+        <v>1478.0</v>
       </c>
     </row>
     <row r="47">
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1720.0</v>
+        <v>1726.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1154,10 +1154,10 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>773.0</v>
+        <v>776.0</v>
       </c>
       <c r="D51" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="52">
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="D54" t="n">
         <v>185.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>446.0</v>
+        <v>447.0</v>
       </c>
       <c r="D56" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="57">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1861.0</v>
+        <v>1863.0</v>
       </c>
       <c r="D59" t="n">
         <v>366.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1440.0</v>
+        <v>1442.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13445.0</v>
+        <v>13457.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1516.0</v>
+        <v>1519.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2761.0</v>
+        <v>2764.0</v>
       </c>
     </row>
     <row r="65">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>830.0</v>
+        <v>833.0</v>
       </c>
       <c r="D89" t="n">
         <v>144.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>869.0</v>
+        <v>871.0</v>
       </c>
       <c r="D96" t="n">
-        <v>489.0</v>
+        <v>490.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
   <si>
     <t>Region</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>Agrigento</t>
+  </si>
+  <si>
+    <t>Caltanissetta</t>
   </si>
   <si>
     <t>Catania</t>
@@ -818,7 +821,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="D27" t="n">
         <v>12.0</v>
@@ -832,7 +835,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="D28" t="n">
         <v>166.0</v>
@@ -916,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4031.0</v>
+        <v>4033.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -930,7 +933,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>989.0</v>
+        <v>990.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -958,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>291.0</v>
+        <v>297.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1266,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1863.0</v>
+        <v>1868.0</v>
       </c>
       <c r="D59" t="n">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1803.0</v>
+        <v>1825.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1442.0</v>
+        <v>1456.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13457.0</v>
+        <v>13477.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1342,7 @@
         <v>1519.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2764.0</v>
+        <v>2766.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1370,7 @@
         <v>1612.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1196.0</v>
+        <v>1204.0</v>
       </c>
     </row>
     <row r="67">
@@ -1574,10 +1577,10 @@
         <v>104</v>
       </c>
       <c r="C81" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="D81" t="n">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="82">
@@ -1588,10 +1591,10 @@
         <v>105</v>
       </c>
       <c r="C82" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="D82" t="n">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="83">
@@ -1602,10 +1605,10 @@
         <v>106</v>
       </c>
       <c r="C83" t="n">
-        <v>53.0</v>
+        <v>3.0</v>
       </c>
       <c r="D83" t="n">
-        <v>184.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="84">
@@ -1619,7 +1622,7 @@
         <v>53.0</v>
       </c>
       <c r="D84" t="n">
-        <v>4.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="85">
@@ -1630,10 +1633,10 @@
         <v>108</v>
       </c>
       <c r="C85" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="D85" t="n">
         <v>4.0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>19.0</v>
       </c>
     </row>
     <row r="86">
@@ -1644,10 +1647,10 @@
         <v>109</v>
       </c>
       <c r="C86" t="n">
-        <v>44.0</v>
+        <v>4.0</v>
       </c>
       <c r="D86" t="n">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="87">
@@ -1658,24 +1661,24 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>12.0</v>
+        <v>44.0</v>
       </c>
       <c r="D87" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>530.0</v>
+        <v>12.0</v>
       </c>
       <c r="D88" t="n">
-        <v>295.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,10 +1689,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>833.0</v>
+        <v>531.0</v>
       </c>
       <c r="D89" t="n">
-        <v>144.0</v>
+        <v>295.0</v>
       </c>
     </row>
     <row r="90">
@@ -1700,10 +1703,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>316.0</v>
+        <v>865.0</v>
       </c>
       <c r="D90" t="n">
-        <v>117.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="91">
@@ -1714,10 +1717,10 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>182.0</v>
+        <v>317.0</v>
       </c>
       <c r="D91" t="n">
-        <v>71.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="92">
@@ -1728,10 +1731,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>5.0</v>
+        <v>182.0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="93">
@@ -1742,10 +1745,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>302.0</v>
+        <v>5.0</v>
       </c>
       <c r="D93" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,10 +1759,10 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>32.0</v>
+        <v>307.0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="95">
@@ -1770,24 +1773,24 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>179.0</v>
+        <v>34.0</v>
       </c>
       <c r="D95" t="n">
-        <v>239.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B96" t="s">
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>871.0</v>
+        <v>179.0</v>
       </c>
       <c r="D96" t="n">
-        <v>490.0</v>
+        <v>239.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,38 +1801,38 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>628.0</v>
+        <v>871.0</v>
       </c>
       <c r="D97" t="n">
-        <v>157.0</v>
+        <v>490.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B98" t="s">
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>97.0</v>
+        <v>628.0</v>
       </c>
       <c r="D98" t="n">
-        <v>44.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99" t="s">
         <v>122</v>
       </c>
       <c r="C99" t="n">
-        <v>32.0</v>
+        <v>97.0</v>
       </c>
       <c r="D99" t="n">
-        <v>228.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,10 +1843,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>239.0</v>
+        <v>32.0</v>
       </c>
       <c r="D100" t="n">
-        <v>162.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="101">
@@ -1854,10 +1857,10 @@
         <v>124</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0</v>
+        <v>241.0</v>
       </c>
       <c r="D101" t="n">
-        <v>113.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="102">
@@ -1868,10 +1871,10 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D102" t="n">
         <v>113.0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>201.0</v>
       </c>
     </row>
     <row r="103">
@@ -1882,10 +1885,10 @@
         <v>126</v>
       </c>
       <c r="C103" t="n">
-        <v>10.0</v>
+        <v>113.0</v>
       </c>
       <c r="D103" t="n">
-        <v>134.0</v>
+        <v>201.0</v>
       </c>
     </row>
     <row r="104">
@@ -1896,10 +1899,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>130.0</v>
+        <v>10.0</v>
       </c>
       <c r="D104" t="n">
-        <v>326.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,10 +1913,24 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>92.0</v>
+        <v>130.0</v>
       </c>
       <c r="D105" t="n">
-        <v>196.0</v>
+        <v>326.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>24</v>
+      </c>
+      <c r="B106" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>199.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>711.0</v>
+        <v>730.0</v>
       </c>
       <c r="D18" t="n">
         <v>244.0</v>
@@ -737,10 +737,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>458.0</v>
+        <v>490.0</v>
       </c>
       <c r="D21" t="n">
-        <v>548.0</v>
+        <v>549.0</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +751,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="D22" t="n">
         <v>296.0</v>
@@ -782,7 +782,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>398.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="D25" t="n">
         <v>306.0</v>
@@ -877,7 +877,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>975.0</v>
+        <v>978.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -989,7 +989,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>737.0</v>
+        <v>769.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1456.0</v>
+        <v>1465.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13477.0</v>
+        <v>13490.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2914.0</v>
       </c>
       <c r="D63" t="n">
-        <v>707.0</v>
+        <v>709.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1519.0</v>
+        <v>1521.0</v>
       </c>
       <c r="D64" t="n">
         <v>2766.0</v>
@@ -1689,10 +1689,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
       <c r="D89" t="n">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
     </row>
     <row r="90">
@@ -1703,10 +1703,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>865.0</v>
+        <v>950.0</v>
       </c>
       <c r="D90" t="n">
-        <v>146.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="91">
@@ -1731,10 +1731,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>182.0</v>
+        <v>185.0</v>
       </c>
       <c r="D92" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="93">
@@ -1759,10 +1759,10 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>307.0</v>
+        <v>310.0</v>
       </c>
       <c r="D94" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="95">
@@ -1773,7 +1773,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="D95" t="n">
         <v>0.0</v>
@@ -1787,7 +1787,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="D96" t="n">
         <v>239.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4033.0</v>
+        <v>4034.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -1174,7 +1174,7 @@
         <v>395.0</v>
       </c>
       <c r="D52" t="n">
-        <v>108.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="53">
@@ -1227,7 +1227,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="D56" t="n">
         <v>152.0</v>
@@ -1269,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1868.0</v>
+        <v>1871.0</v>
       </c>
       <c r="D59" t="n">
-        <v>367.0</v>
+        <v>369.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1825.0</v>
+        <v>1836.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1465.0</v>
+        <v>1485.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13490.0</v>
+        <v>13510.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2914.0</v>
       </c>
       <c r="D63" t="n">
-        <v>709.0</v>
+        <v>710.0</v>
       </c>
     </row>
     <row r="64">
@@ -1342,7 +1342,7 @@
         <v>1521.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2766.0</v>
+        <v>2768.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1612.0</v>
+        <v>1613.0</v>
       </c>
       <c r="D66" t="n">
         <v>1204.0</v>
@@ -1717,7 +1717,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="D91" t="n">
         <v>117.0</v>
@@ -1773,7 +1773,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="D95" t="n">
         <v>0.0</v>
@@ -1801,7 +1801,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>871.0</v>
+        <v>877.0</v>
       </c>
       <c r="D97" t="n">
         <v>490.0</v>
@@ -1815,7 +1815,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>628.0</v>
+        <v>629.0</v>
       </c>
       <c r="D98" t="n">
         <v>157.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -527,7 +527,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1209.0</v>
+        <v>1232.0</v>
       </c>
       <c r="D6" t="n">
         <v>345.0</v>
@@ -541,10 +541,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2263.0</v>
+        <v>2285.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1107.0</v>
+        <v>1112.0</v>
       </c>
     </row>
     <row r="8">
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4034.0</v>
+        <v>4038.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -1409,10 +1409,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>232.0</v>
+        <v>238.0</v>
       </c>
       <c r="D69" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
     </row>
     <row r="70">
@@ -1440,7 +1440,7 @@
         <v>3.0</v>
       </c>
       <c r="D71" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="72">
@@ -1479,7 +1479,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>310.0</v>
+        <v>313.0</v>
       </c>
       <c r="D74" t="n">
         <v>51.0</v>
@@ -1717,7 +1717,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>318.0</v>
+        <v>319.0</v>
       </c>
       <c r="D91" t="n">
         <v>117.0</v>
@@ -1734,7 +1734,7 @@
         <v>185.0</v>
       </c>
       <c r="D92" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="93">
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="D94" t="n">
         <v>53.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -765,10 +765,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0</v>
+        <v>47.0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="24">
@@ -793,10 +793,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>127.0</v>
+        <v>222.0</v>
       </c>
       <c r="D25" t="n">
-        <v>306.0</v>
+        <v>353.0</v>
       </c>
     </row>
     <row r="26">
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>297.0</v>
+        <v>314.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1076,7 +1076,7 @@
         <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24888.0</v>
+        <v>24889.0</v>
       </c>
     </row>
     <row r="46">
@@ -1129,10 +1129,10 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1726.0</v>
+        <v>2390.0</v>
       </c>
       <c r="D49" t="n">
-        <v>3904.0</v>
+        <v>19020.0</v>
       </c>
     </row>
     <row r="50">
@@ -1269,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1871.0</v>
+        <v>1927.0</v>
       </c>
       <c r="D59" t="n">
         <v>369.0</v>
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1836.0</v>
+        <v>1845.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1300,7 +1300,7 @@
         <v>739.0</v>
       </c>
       <c r="D61" t="n">
-        <v>925.0</v>
+        <v>927.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1485.0</v>
+        <v>1510.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13510.0</v>
+        <v>13517.0</v>
       </c>
     </row>
     <row r="63">
@@ -1342,7 +1342,7 @@
         <v>1521.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2768.0</v>
+        <v>2770.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1613.0</v>
+        <v>1616.0</v>
       </c>
       <c r="D66" t="n">
         <v>1204.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>730.0</v>
+        <v>809.0</v>
       </c>
       <c r="D18" t="n">
         <v>244.0</v>
@@ -737,7 +737,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>490.0</v>
+        <v>524.0</v>
       </c>
       <c r="D21" t="n">
         <v>549.0</v>
@@ -751,7 +751,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="D22" t="n">
         <v>296.0</v>
@@ -793,10 +793,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="D25" t="n">
-        <v>353.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="26">
@@ -891,7 +891,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4038.0</v>
+        <v>4040.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -933,7 +933,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>990.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -989,7 +989,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>769.0</v>
+        <v>791.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1006,7 +1006,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n">
-        <v>965.0</v>
+        <v>971.0</v>
       </c>
     </row>
     <row r="41">
@@ -1020,7 +1020,7 @@
         <v>188.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2213.0</v>
+        <v>2220.0</v>
       </c>
     </row>
     <row r="42">
@@ -1031,7 +1031,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1045,10 +1045,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4017.0</v>
+        <v>4018.0</v>
       </c>
     </row>
     <row r="44">
@@ -1076,7 +1076,7 @@
         <v>87.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24889.0</v>
+        <v>24890.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,10 +1087,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1478.0</v>
+        <v>1479.0</v>
       </c>
     </row>
     <row r="47">
@@ -1101,7 +1101,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>761.0</v>
+        <v>763.0</v>
       </c>
       <c r="D47" t="n">
         <v>1899.0</v>
@@ -1129,10 +1129,10 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>2390.0</v>
+        <v>2393.0</v>
       </c>
       <c r="D49" t="n">
-        <v>19020.0</v>
+        <v>19031.0</v>
       </c>
     </row>
     <row r="50">
@@ -1216,7 +1216,7 @@
         <v>512.0</v>
       </c>
       <c r="D55" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="56">
@@ -1227,7 +1227,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>448.0</v>
+        <v>449.0</v>
       </c>
       <c r="D56" t="n">
         <v>152.0</v>
@@ -1269,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1927.0</v>
+        <v>1928.0</v>
       </c>
       <c r="D59" t="n">
-        <v>369.0</v>
+        <v>370.0</v>
       </c>
     </row>
     <row r="60">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1510.0</v>
+        <v>1512.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13517.0</v>
+        <v>13526.0</v>
       </c>
     </row>
     <row r="63">
@@ -1342,7 +1342,7 @@
         <v>1521.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2770.0</v>
+        <v>2772.0</v>
       </c>
     </row>
     <row r="65">
@@ -1370,7 +1370,7 @@
         <v>1616.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1204.0</v>
+        <v>1206.0</v>
       </c>
     </row>
     <row r="67">
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>950.0</v>
+        <v>960.0</v>
       </c>
       <c r="D90" t="n">
         <v>149.0</v>
@@ -1815,7 +1815,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>629.0</v>
+        <v>630.0</v>
       </c>
       <c r="D98" t="n">
         <v>157.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -835,7 +835,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="D28" t="n">
         <v>166.0</v>
@@ -866,7 +866,7 @@
         <v>185.0</v>
       </c>
       <c r="D30" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="31">
@@ -905,7 +905,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4040.0</v>
+        <v>4044.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>314.0</v>
+        <v>325.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1269,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1928.0</v>
+        <v>1930.0</v>
       </c>
       <c r="D59" t="n">
         <v>370.0</v>
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1845.0</v>
+        <v>1849.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1512.0</v>
+        <v>1522.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13526.0</v>
+        <v>13527.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1521.0</v>
+        <v>1523.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2772.0</v>
+        <v>2775.0</v>
       </c>
     </row>
     <row r="65">
@@ -1370,7 +1370,7 @@
         <v>1616.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1206.0</v>
+        <v>1212.0</v>
       </c>
     </row>
     <row r="67">
@@ -1384,7 +1384,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>600.0</v>
+        <v>604.0</v>
       </c>
     </row>
     <row r="68">
@@ -1692,7 +1692,7 @@
         <v>532.0</v>
       </c>
       <c r="D89" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
     </row>
     <row r="90">
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>960.0</v>
+        <v>1032.0</v>
       </c>
       <c r="D90" t="n">
         <v>149.0</v>
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
       <c r="D94" t="n">
         <v>53.0</v>
@@ -1773,7 +1773,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="D95" t="n">
         <v>0.0</v>
@@ -1790,7 +1790,7 @@
         <v>180.0</v>
       </c>
       <c r="D96" t="n">
-        <v>239.0</v>
+        <v>241.0</v>
       </c>
     </row>
     <row r="97">
@@ -1916,7 +1916,7 @@
         <v>130.0</v>
       </c>
       <c r="D105" t="n">
-        <v>326.0</v>
+        <v>328.0</v>
       </c>
     </row>
     <row r="106">
@@ -1927,10 +1927,10 @@
         <v>129</v>
       </c>
       <c r="C106" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="D106" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -695,10 +695,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>809.0</v>
+        <v>830.0</v>
       </c>
       <c r="D18" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="19">
@@ -740,7 +740,7 @@
         <v>524.0</v>
       </c>
       <c r="D21" t="n">
-        <v>549.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
         <v>44.0</v>
       </c>
       <c r="D22" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
     </row>
     <row r="23">
@@ -768,7 +768,7 @@
         <v>47.0</v>
       </c>
       <c r="D23" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="24">
@@ -793,7 +793,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="D25" t="n">
         <v>358.0</v>
@@ -810,7 +810,7 @@
         <v>28.0</v>
       </c>
       <c r="D26" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="27">
@@ -877,7 +877,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>978.0</v>
+        <v>979.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4044.0</v>
+        <v>4045.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>325.0</v>
+        <v>328.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -989,7 +989,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>791.0</v>
+        <v>815.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1269,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1930.0</v>
+        <v>1933.0</v>
       </c>
       <c r="D59" t="n">
         <v>370.0</v>
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1849.0</v>
+        <v>1866.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1300,7 +1300,7 @@
         <v>739.0</v>
       </c>
       <c r="D61" t="n">
-        <v>927.0</v>
+        <v>929.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1522.0</v>
+        <v>1537.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13527.0</v>
+        <v>13539.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1523.0</v>
+        <v>1524.0</v>
       </c>
       <c r="D64" t="n">
         <v>2775.0</v>
@@ -1367,10 +1367,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1616.0</v>
+        <v>1617.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1212.0</v>
+        <v>1214.0</v>
       </c>
     </row>
     <row r="67">
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>532.0</v>
+        <v>533.0</v>
       </c>
       <c r="D89" t="n">
         <v>297.0</v>
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>1032.0</v>
+        <v>1077.0</v>
       </c>
       <c r="D90" t="n">
         <v>149.0</v>
@@ -1734,7 +1734,7 @@
         <v>185.0</v>
       </c>
       <c r="D92" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="93">
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>316.0</v>
+        <v>326.0</v>
       </c>
       <c r="D94" t="n">
         <v>53.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -527,10 +527,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1232.0</v>
+        <v>1243.0</v>
       </c>
       <c r="D6" t="n">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
     </row>
     <row r="7">
@@ -541,7 +541,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2285.0</v>
+        <v>2287.0</v>
       </c>
       <c r="D7" t="n">
         <v>1112.0</v>
@@ -877,7 +877,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>979.0</v>
+        <v>983.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>4045.0</v>
+        <v>4052.0</v>
       </c>
       <c r="D34" t="n">
         <v>193.0</v>
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -992,7 +992,7 @@
         <v>815.0</v>
       </c>
       <c r="D39" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="40">
@@ -1171,7 +1171,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="D52" t="n">
         <v>110.0</v>
@@ -1202,7 +1202,7 @@
         <v>108.0</v>
       </c>
       <c r="D54" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="55">
@@ -1216,7 +1216,7 @@
         <v>512.0</v>
       </c>
       <c r="D55" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="56">
@@ -1230,7 +1230,7 @@
         <v>449.0</v>
       </c>
       <c r="D56" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="57">
@@ -1269,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1933.0</v>
+        <v>1934.0</v>
       </c>
       <c r="D59" t="n">
         <v>370.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1537.0</v>
+        <v>1549.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13539.0</v>
+        <v>13565.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2914.0</v>
       </c>
       <c r="D63" t="n">
-        <v>710.0</v>
+        <v>711.0</v>
       </c>
     </row>
     <row r="64">
@@ -1342,7 +1342,7 @@
         <v>1524.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2775.0</v>
+        <v>2777.0</v>
       </c>
     </row>
     <row r="65">
@@ -1370,7 +1370,7 @@
         <v>1617.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1214.0</v>
+        <v>1217.0</v>
       </c>
     </row>
     <row r="67">
@@ -1409,7 +1409,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>238.0</v>
+        <v>240.0</v>
       </c>
       <c r="D69" t="n">
         <v>210.0</v>
@@ -1451,7 +1451,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="D72" t="n">
         <v>0.0</v>
@@ -1479,7 +1479,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>313.0</v>
+        <v>317.0</v>
       </c>
       <c r="D74" t="n">
         <v>51.0</v>
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>533.0</v>
+        <v>534.0</v>
       </c>
       <c r="D89" t="n">
         <v>297.0</v>
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>1077.0</v>
+        <v>1116.0</v>
       </c>
       <c r="D90" t="n">
         <v>149.0</v>
@@ -1717,7 +1717,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="D91" t="n">
         <v>117.0</v>
@@ -1731,7 +1731,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>185.0</v>
+        <v>187.0</v>
       </c>
       <c r="D92" t="n">
         <v>75.0</v>
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>326.0</v>
+        <v>328.0</v>
       </c>
       <c r="D94" t="n">
         <v>53.0</v>
@@ -1787,7 +1787,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="D96" t="n">
         <v>241.0</v>
@@ -1801,7 +1801,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>877.0</v>
+        <v>883.0</v>
       </c>
       <c r="D97" t="n">
         <v>490.0</v>
@@ -1815,7 +1815,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="D98" t="n">
         <v>157.0</v>
